--- a/public/files/formato_productos.xlsx
+++ b/public/files/formato_productos.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9075"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="16">
   <si>
     <t/>
   </si>
@@ -55,6 +55,18 @@
   </si>
   <si>
     <t>CÓDIGO*</t>
+  </si>
+  <si>
+    <t>CARACTERISTICAS</t>
+  </si>
+  <si>
+    <t>CALIDAD*</t>
+  </si>
+  <si>
+    <t>COBERTURA</t>
+  </si>
+  <si>
+    <t>FORMATO</t>
   </si>
 </sst>
 </file>
@@ -432,28 +444,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -470,25 +486,37 @@
         <v>7</v>
       </c>
       <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,18 +532,6 @@
       <c r="E2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" t="s">
-        <v>0</v>
-      </c>
       <c r="J2" t="s">
         <v>0</v>
       </c>
@@ -541,13 +557,26 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A2 B2:I2 J2:R2" numberStoredAsText="1"/>
+    <ignoredError sqref="J2:V2 A2:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>